--- a/software/src/python_code/arduino-data.xlsx
+++ b/software/src/python_code/arduino-data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30431"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E446AE0-6A90-4DC5-9875-3C420641179A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F006240E-5F80-46DE-B5AA-8CDA78841580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>time_ms</t>
   </si>
@@ -43,6 +43,12 @@
   </si>
   <si>
     <t>sensor2</t>
+  </si>
+  <si>
+    <t>sensor3</t>
+  </si>
+  <si>
+    <t>sensor4</t>
   </si>
 </sst>
 </file>
@@ -394,10 +400,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -407,8 +413,14 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>0</v>
       </c>
@@ -418,8 +430,14 @@
       <c r="C2">
         <v>775</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <v>779</v>
+      </c>
+      <c r="E2">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>500</v>
       </c>
@@ -429,8 +447,14 @@
       <c r="C3">
         <v>812</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3">
+        <v>833</v>
+      </c>
+      <c r="E3">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1000</v>
       </c>
@@ -440,8 +464,14 @@
       <c r="C4">
         <v>804</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4">
+        <v>792</v>
+      </c>
+      <c r="E4">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1500</v>
       </c>
@@ -451,8 +481,14 @@
       <c r="C5">
         <v>786</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5">
+        <v>812</v>
+      </c>
+      <c r="E5">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>2000</v>
       </c>
@@ -462,8 +498,14 @@
       <c r="C6">
         <v>793</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6">
+        <v>789</v>
+      </c>
+      <c r="E6">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>2500</v>
       </c>
@@ -473,8 +515,14 @@
       <c r="C7">
         <v>807</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7">
+        <v>772</v>
+      </c>
+      <c r="E7">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>3000</v>
       </c>
@@ -484,8 +532,14 @@
       <c r="C8">
         <v>819</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8">
+        <v>804</v>
+      </c>
+      <c r="E8">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>3500</v>
       </c>
@@ -495,8 +549,14 @@
       <c r="C9">
         <v>772</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9">
+        <v>816</v>
+      </c>
+      <c r="E9">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>4000</v>
       </c>
@@ -504,6 +564,216 @@
         <v>827</v>
       </c>
       <c r="C10">
+        <v>786</v>
+      </c>
+      <c r="D10">
+        <v>827</v>
+      </c>
+      <c r="E10">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>4500</v>
+      </c>
+      <c r="B11">
+        <v>815</v>
+      </c>
+      <c r="C11">
+        <v>792</v>
+      </c>
+      <c r="D11">
+        <v>805</v>
+      </c>
+      <c r="E11">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <v>5000</v>
+      </c>
+      <c r="B12">
+        <v>780</v>
+      </c>
+      <c r="C12">
+        <v>798</v>
+      </c>
+      <c r="D12">
+        <v>790</v>
+      </c>
+      <c r="E12">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <v>5500</v>
+      </c>
+      <c r="B13">
+        <v>804</v>
+      </c>
+      <c r="C13">
+        <v>814</v>
+      </c>
+      <c r="D13">
+        <v>794</v>
+      </c>
+      <c r="E13">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>6000</v>
+      </c>
+      <c r="B14">
+        <v>802</v>
+      </c>
+      <c r="C14">
+        <v>786</v>
+      </c>
+      <c r="D14">
+        <v>792</v>
+      </c>
+      <c r="E14">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>6500</v>
+      </c>
+      <c r="B15">
+        <v>793</v>
+      </c>
+      <c r="C15">
+        <v>782</v>
+      </c>
+      <c r="D15">
+        <v>803</v>
+      </c>
+      <c r="E15">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>7000</v>
+      </c>
+      <c r="B16">
+        <v>784</v>
+      </c>
+      <c r="C16">
+        <v>779</v>
+      </c>
+      <c r="D16">
+        <v>794</v>
+      </c>
+      <c r="E16">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>7500</v>
+      </c>
+      <c r="B17">
+        <v>796</v>
+      </c>
+      <c r="C17">
+        <v>817</v>
+      </c>
+      <c r="D17">
+        <v>803</v>
+      </c>
+      <c r="E17">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>8000</v>
+      </c>
+      <c r="B18">
+        <v>794</v>
+      </c>
+      <c r="C18">
+        <v>807</v>
+      </c>
+      <c r="D18">
+        <v>794</v>
+      </c>
+      <c r="E18">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>8500</v>
+      </c>
+      <c r="B19">
+        <v>812</v>
+      </c>
+      <c r="C19">
+        <v>786</v>
+      </c>
+      <c r="D19">
+        <v>787</v>
+      </c>
+      <c r="E19">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>9000</v>
+      </c>
+      <c r="B20">
+        <v>816</v>
+      </c>
+      <c r="C20">
+        <v>801</v>
+      </c>
+      <c r="D20">
+        <v>805</v>
+      </c>
+      <c r="E20">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>9500</v>
+      </c>
+      <c r="B21">
+        <v>806</v>
+      </c>
+      <c r="C21">
+        <v>794</v>
+      </c>
+      <c r="D21">
+        <v>814</v>
+      </c>
+      <c r="E21">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>10000</v>
+      </c>
+      <c r="B22">
+        <v>797</v>
+      </c>
+      <c r="C22">
+        <v>808</v>
+      </c>
+      <c r="D22">
+        <v>796</v>
+      </c>
+      <c r="E22">
         <v>786</v>
       </c>
     </row>
